--- a/samples/sample_2/SAFE_VESSELS_INVENTORY_20251201.XLSX
+++ b/samples/sample_2/SAFE_VESSELS_INVENTORY_20251201.XLSX
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t xml:space="preserve">SHIPID</t>
   </si>
@@ -45,37 +45,67 @@
     <t xml:space="preserve">DESCRIP</t>
   </si>
   <si>
-    <t xml:space="preserve">SH_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Ship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUST_001  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basic item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nice item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">good item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fast Ship</t>
+    <t xml:space="preserve">ship 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eagle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cust 001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 (3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ship 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ship 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falcon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 (1)</t>
   </si>
 </sst>
 </file>
@@ -160,20 +190,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -181,7 +203,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,204 +403,309 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G335"/>
+  <dimension ref="A1:G336"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="0" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E326" s="5"/>
-      <c r="F326" s="5"/>
-    </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E327" s="5"/>
-      <c r="F327" s="5"/>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E328" s="5"/>
-      <c r="F328" s="5"/>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E329" s="5"/>
-      <c r="F329" s="5"/>
-    </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E330" s="5"/>
-      <c r="F330" s="5"/>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E331" s="5"/>
-      <c r="F331" s="5"/>
-    </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E332" s="5"/>
-      <c r="F332" s="5"/>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E333" s="5"/>
-      <c r="F333" s="5"/>
-    </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E334" s="5"/>
-      <c r="F334" s="5"/>
-    </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E335" s="5"/>
-      <c r="F335" s="5"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E327" s="4"/>
+      <c r="F327" s="4"/>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E328" s="4"/>
+      <c r="F328" s="4"/>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E329" s="4"/>
+      <c r="F329" s="4"/>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E330" s="4"/>
+      <c r="F330" s="4"/>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E331" s="4"/>
+      <c r="F331" s="4"/>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E332" s="4"/>
+      <c r="F332" s="4"/>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E333" s="4"/>
+      <c r="F333" s="4"/>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E334" s="4"/>
+      <c r="F334" s="4"/>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E335" s="4"/>
+      <c r="F335" s="4"/>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E336" s="4"/>
+      <c r="F336" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -592,7 +723,7 @@
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -610,7 +741,7 @@
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
